--- a/data/trans_orig/IP31C_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34347</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31109</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>45279</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>41566</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>41707</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38331</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>43488</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>86,78%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>156</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86986</t>
+          <t>75913</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83826</t>
+          <t>72463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88774</t>
+          <t>77402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2198</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5840</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36545</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36545</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36545</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>45279</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45279</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>45279</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44171</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44171</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44171</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>89450</t>
+          <t>78111</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89450</t>
+          <t>78111</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89450</t>
+          <t>78111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>142176</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>134293</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>147239</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>152089</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>146969</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>155458</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>165655</t>
+          <t>138809</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>157864</t>
+          <t>133592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>170905</t>
+          <t>141961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>317745</t>
+          <t>280986</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309040</t>
+          <t>273564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324910</t>
+          <t>287858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1492</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6538</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2444</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>339</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8551</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20818</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5910</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11081</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28968</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>158395</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>158395</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>158395</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>340355</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>340355</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340355</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>184447</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>175693</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>190704</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>92,17%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>87,79%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>95,29%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>151845</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>143749</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>158523</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>87,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>197527</t>
+          <t>151783</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189584</t>
+          <t>142862</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>203291</t>
+          <t>159200</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>349373</t>
+          <t>336230</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>337607</t>
+          <t>325073</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>358523</t>
+          <t>346778</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>847</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14717</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8922</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22993</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>20433</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13884</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28393</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>14639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>36759</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46061</t>
+          <t>47919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>250786</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>237889</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>260832</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>86,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>221271</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>152971</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>248199</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>80,68%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>55,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>264738</t>
+          <t>224626</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251834</t>
+          <t>211254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>276120</t>
+          <t>232878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>486011</t>
+          <t>475412</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>403862</t>
+          <t>459651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>515491</t>
+          <t>489805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31299</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105476</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124716</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>35470</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>26034</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46713</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>21697</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13868</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>32570</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>16538</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45451</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>55867</t>
+          <t>58869</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>47030</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71281</t>
+          <t>73684</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>291359</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>291359</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>291359</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>578458</t>
+          <t>546696</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>578458</t>
+          <t>546696</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>578458</t>
+          <t>546696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>611755</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>594838</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>624783</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>89,3%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>839</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>570485</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>478345</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>600018</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>87,63%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>73,48%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>669628</t>
+          <t>556785</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>653190</t>
+          <t>542670</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>683723</t>
+          <t>570142</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1240114</t>
+          <t>1168540</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1143772</t>
+          <t>1147396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1271892</t>
+          <t>1188085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7556</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>14744</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>32489</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>140049</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>28666</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>65760</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>53259</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>81355</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>48040</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>36228</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>61083</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>51030</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>39027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80544</t>
+          <t>62612</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>116791</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96021</t>
+          <t>99650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134031</t>
+          <t>137397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
